--- a/data/dividends_info_20260308.xlsx
+++ b/data/dividends_info_20260308.xlsx
@@ -2528,7 +2528,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2538,14 +2538,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2555,14 +2555,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2596,7 +2596,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2613,7 +2613,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2623,14 +2623,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2647,7 +2647,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2657,14 +2657,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2681,7 +2681,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2691,14 +2691,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2708,14 +2708,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2732,7 +2732,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2742,14 +2742,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2766,7 +2766,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2776,14 +2776,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2793,14 +2793,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2810,14 +2810,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2834,7 +2834,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sesa S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2844,14 +2844,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Sesa S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2861,14 +2861,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2878,14 +2878,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2902,7 +2902,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2919,7 +2919,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2936,7 +2936,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2963,14 +2963,14 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2987,7 +2987,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3089,7 +3089,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3106,7 +3106,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3116,14 +3116,14 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -3286,14 +3286,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3310,7 +3310,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3337,14 +3337,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3361,7 +3361,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3378,7 +3378,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3388,14 +3388,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3412,7 +3412,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3439,14 +3439,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3463,7 +3463,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3473,14 +3473,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3497,7 +3497,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3667,7 +3667,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3677,14 +3677,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3837,7 +3837,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3854,7 +3854,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3905,7 +3905,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3922,7 +3922,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3932,14 +3932,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3949,14 +3949,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3966,14 +3966,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4000,14 +4000,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4017,14 +4017,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4075,7 +4075,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4085,14 +4085,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4109,7 +4109,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4119,14 +4119,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4160,7 +4160,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4170,14 +4170,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4194,7 +4194,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4204,14 +4204,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4228,7 +4228,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4255,14 +4255,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4272,14 +4272,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4306,14 +4306,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4323,14 +4323,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4347,7 +4347,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4357,14 +4357,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4374,14 +4374,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4398,7 +4398,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4415,7 +4415,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4425,14 +4425,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4442,14 +4442,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4466,7 +4466,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4483,7 +4483,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4493,14 +4493,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4517,7 +4517,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4534,7 +4534,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4568,7 +4568,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4585,7 +4585,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4619,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4636,7 +4636,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4653,7 +4653,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4670,7 +4670,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4704,7 +4704,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4721,7 +4721,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4738,7 +4738,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4755,7 +4755,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4772,7 +4772,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4789,7 +4789,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4799,14 +4799,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4840,7 +4840,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4857,7 +4857,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4874,7 +4874,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4891,7 +4891,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4908,7 +4908,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4925,7 +4925,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4942,7 +4942,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4959,7 +4959,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4976,7 +4976,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4993,7 +4993,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5010,7 +5010,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5020,14 +5020,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5044,7 +5044,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5061,7 +5061,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -5078,7 +5078,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5095,7 +5095,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5112,7 +5112,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5129,7 +5129,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5197,7 +5197,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5214,7 +5214,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5224,14 +5224,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5248,7 +5248,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5258,14 +5258,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5282,7 +5282,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5316,7 +5316,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5333,7 +5333,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5350,7 +5350,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5360,14 +5360,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5384,7 +5384,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5401,7 +5401,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5418,7 +5418,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5435,7 +5435,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5452,7 +5452,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5462,14 +5462,14 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5486,7 +5486,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5496,14 +5496,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5513,14 +5513,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5537,7 +5537,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5547,14 +5547,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5571,7 +5571,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5588,7 +5588,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5622,7 +5622,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5632,14 +5632,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5656,7 +5656,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5673,7 +5673,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5690,7 +5690,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5707,7 +5707,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5717,14 +5717,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5734,14 +5734,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5758,7 +5758,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5768,14 +5768,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5792,7 +5792,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5809,7 +5809,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5819,14 +5819,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5836,14 +5836,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5853,14 +5853,14 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5877,7 +5877,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5894,7 +5894,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5904,14 +5904,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5928,7 +5928,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5945,7 +5945,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5955,14 +5955,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5979,7 +5979,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5989,14 +5989,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6006,14 +6006,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6023,14 +6023,14 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6047,7 +6047,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6057,14 +6057,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6081,7 +6081,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6098,7 +6098,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6115,7 +6115,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6132,7 +6132,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6142,14 +6142,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6159,14 +6159,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6200,7 +6200,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6217,7 +6217,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6227,14 +6227,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6251,7 +6251,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6268,7 +6268,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6285,7 +6285,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6302,7 +6302,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6319,7 +6319,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6336,7 +6336,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6353,7 +6353,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6370,7 +6370,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6387,7 +6387,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6404,7 +6404,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6421,7 +6421,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6438,7 +6438,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6472,7 +6472,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6489,7 +6489,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6506,7 +6506,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6523,7 +6523,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6540,7 +6540,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6550,14 +6550,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6574,7 +6574,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6584,14 +6584,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6608,7 +6608,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6625,7 +6625,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6642,7 +6642,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6659,7 +6659,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6676,7 +6676,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6693,7 +6693,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6727,7 +6727,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6744,7 +6744,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6778,7 +6778,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6795,7 +6795,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6812,7 +6812,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6829,7 +6829,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6839,14 +6839,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6863,7 +6863,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6880,7 +6880,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6897,7 +6897,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6914,7 +6914,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>HEALTH ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6948,7 +6948,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6965,7 +6965,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6982,7 +6982,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6999,7 +6999,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7016,7 +7016,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7033,7 +7033,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7043,14 +7043,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7084,7 +7084,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7101,7 +7101,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7118,7 +7118,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7135,7 +7135,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7145,14 +7145,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7169,7 +7169,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7179,14 +7179,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7203,7 +7203,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7213,14 +7213,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7230,14 +7230,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7254,7 +7254,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7271,7 +7271,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7288,7 +7288,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7305,7 +7305,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7322,7 +7322,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7339,7 +7339,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7356,7 +7356,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -7373,7 +7373,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -7390,7 +7390,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7407,7 +7407,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7441,7 +7441,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7458,7 +7458,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7468,14 +7468,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7492,7 +7492,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7509,7 +7509,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7519,14 +7519,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7543,7 +7543,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7553,14 +7553,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7570,14 +7570,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7594,7 +7594,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7611,7 +7611,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>HEALTH ITALIA S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7628,7 +7628,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7645,7 +7645,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7662,7 +7662,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7679,7 +7679,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7713,7 +7713,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7730,7 +7730,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -7747,7 +7747,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -7764,7 +7764,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -7781,7 +7781,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -7791,14 +7791,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7808,14 +7808,14 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7825,14 +7825,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7849,7 +7849,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7866,7 +7866,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -7876,14 +7876,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7900,7 +7900,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7917,7 +7917,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -7934,7 +7934,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -7961,14 +7961,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -7985,7 +7985,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -7995,14 +7995,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -8019,7 +8019,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -8036,7 +8036,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -8053,7 +8053,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -8063,14 +8063,14 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -8080,14 +8080,14 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -8104,7 +8104,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -8155,7 +8155,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -8172,7 +8172,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -8189,7 +8189,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -8206,7 +8206,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -8223,7 +8223,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -8240,7 +8240,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8250,14 +8250,14 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -8274,7 +8274,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -8284,14 +8284,14 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -8308,7 +8308,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -8325,7 +8325,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -8342,7 +8342,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -8359,7 +8359,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -8369,14 +8369,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -8393,7 +8393,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -8410,7 +8410,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -8420,14 +8420,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -8437,14 +8437,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -8482,61 +8482,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>LU-VE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>